--- a/时间轴照片.xlsx
+++ b/时间轴照片.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11630"/>
+    <workbookView windowWidth="12800" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,162 +32,7 @@
 </file>
 
 <file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
-<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="ID_6B3A95B4242941919AAC84618B53A9B7" descr="微信图片_20261021201051_143_33"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:srcRect l="6372" t="11510" r="14429" b="9327"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3670300" y="0"/>
-          <a:ext cx="1929130" cy="2573020"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="ID_29ABB1E5FDEC4CCAA00BFA4B6467A772" descr="微信图片_20261021201331_214_33"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:srcRect l="10556" t="11192" b="17493"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4384040" y="0"/>
-          <a:ext cx="2808605" cy="3981450"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="ID_87E54543607C4C6A950A0AE4107BBC3D" descr="微信图片_20261021201300_179_33"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5511800" y="952500"/>
-          <a:ext cx="3964940" cy="4507865"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="ID_E069595F04574F7A89C882D6969699D3" descr="微信图片_20261021201050_142_33"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:srcRect l="8918" t="5549" r="17711" b="17586"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6349365" y="952500"/>
-          <a:ext cx="4095750" cy="3219450"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="ID_B8D553F1DAF348F2A56C31AD471A93F9" descr="微信图片_20261021201326_209_33"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5511800" y="1905000"/>
-          <a:ext cx="2114550" cy="2820035"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="ID_AEA56CCA46DC459B95CD4A097C97D735" descr="微信图片_20261021201330_213_33"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId6"/>
-        <a:srcRect l="152" t="9304" r="13909" b="28367"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6349365" y="1905000"/>
-          <a:ext cx="3597275" cy="3479800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-</etc:cellImages>
+<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData"/>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1350,8 +1195,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="3"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="2" width="37.9090909090909" customWidth="1"/>
@@ -1359,48 +1204,24 @@
     <col min="4" max="4" width="13.6363636363636"/>
   </cols>
   <sheetData>
-    <row r="1" ht="75" spans="1:4">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="str">
-        <f>_xlfn.DISPIMG("ID_6B3A95B4242941919AAC84618B53A9B7",1)</f>
-        <v>=DISPIMG("ID_6B3A95B4242941919AAC84618B53A9B7",1)</v>
-      </c>
-      <c r="D1" t="str">
-        <f>_xlfn.DISPIMG("ID_29ABB1E5FDEC4CCAA00BFA4B6467A772",1)</f>
-        <v>=DISPIMG("ID_29ABB1E5FDEC4CCAA00BFA4B6467A772",1)</v>
-      </c>
     </row>
-    <row r="2" ht="75" spans="1:4">
+    <row r="2" spans="1:2">
       <c r="A2" s="1"/>
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="str">
-        <f>_xlfn.DISPIMG("ID_87E54543607C4C6A950A0AE4107BBC3D",1)</f>
-        <v>=DISPIMG("ID_87E54543607C4C6A950A0AE4107BBC3D",1)</v>
-      </c>
-      <c r="D2" t="str">
-        <f>_xlfn.DISPIMG("ID_E069595F04574F7A89C882D6969699D3",1)</f>
-        <v>=DISPIMG("ID_E069595F04574F7A89C882D6969699D3",1)</v>
-      </c>
     </row>
-    <row r="3" ht="75" spans="1:4">
+    <row r="3" spans="1:2">
       <c r="A3" s="1"/>
       <c r="B3" t="s">
         <v>3</v>
-      </c>
-      <c r="C3" t="str">
-        <f>_xlfn.DISPIMG("ID_B8D553F1DAF348F2A56C31AD471A93F9",1)</f>
-        <v>=DISPIMG("ID_B8D553F1DAF348F2A56C31AD471A93F9",1)</v>
-      </c>
-      <c r="D3" t="str">
-        <f>_xlfn.DISPIMG("ID_AEA56CCA46DC459B95CD4A097C97D735",1)</f>
-        <v>=DISPIMG("ID_AEA56CCA46DC459B95CD4A097C97D735",1)</v>
       </c>
     </row>
   </sheetData>

--- a/时间轴照片.xlsx
+++ b/时间轴照片.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="12800" windowHeight="12080"/>
+    <workbookView windowWidth="12800" windowHeight="11630"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Step1：2006-2018——也许我们曾在某处相遇</t>
   </si>
@@ -48,6 +48,44 @@
   </si>
   <si>
     <t>会不会在某个周末我们曾经在庆客隆见过面？会不会某次我在南环广场表演的时候你曾经路过？</t>
+  </si>
+  <si>
+    <t>Step2:2018-2021——“抱歉我好像忘记值日了！”然后我们就认识了！</t>
+  </si>
+  <si>
+    <t>因为初中没什么影像留存（orz你知道的那时候我是个“乖”宝宝（x））只剩下这堆小纸条和存档在记忆里的快乐瞬间了...！</t>
+  </si>
+  <si>
+    <t>Step3:2021-2024——好想能和你聊聊宇宙和天空，聊飞鸟和鲸鱼吹过的季风。拥有了很多deep talk并了解彼此的高中时期</t>
+  </si>
+  <si>
+    <t>依旧小纸条！！坐得近坐得远都在坚持不懈传纸条吗这两个人！很喜欢这种下课回来发现桌子上多了点雷霆小纸条草纸上多了一些画作和话语的感觉......好温馨呐！！</t>
+  </si>
+  <si>
+    <t>网课......两个人连麦到底是为了学习还是截对方丑图做表情包！好萌吧这个小薛思涵！（）</t>
+  </si>
+  <si>
+    <t>全副武装毛茸茸的一个小朋友</t>
+  </si>
+  <si>
+    <t>我熟知的少年们都终将成长/痛哭过大笑过挥挥手去远方/她们会如我祝愿的那样/成为自己的的太阳......
+可恶那天联欢会我怎么没回去拿手机！！只有这几张第三视角糊糊图片惹！
+想念啊想念......</t>
+  </si>
+  <si>
+    <t>萌萌小蘑菇/很帅T的剪刀手（在说什么）/薛老师觉得很赞/看起来好暖和（这张最像我小姨我不行了orzzzz）</t>
+  </si>
+  <si>
+    <t>一眨眼就这样毕业了......一直都特别特别喜欢这张照片，很萌啊两个人很校园那种感觉（本来不就是校园吗喂！！）</t>
+  </si>
+  <si>
+    <t>退校那天仿佛就在昨天一般每一个细节都记得很清楚......有人莫名其妙啃咬zgq莫名其妙抢走班牌有人莫名其妙开始录制vlog，还有甘旭拍照之有人就行（x</t>
+  </si>
+  <si>
+    <t>然后就开始走街串巷在每一场升学宴打扑克...爱化点装大人的烈焰红唇</t>
+  </si>
+  <si>
+    <t>Step4：新生活！关于爱、成长和旅行</t>
   </si>
 </sst>
 </file>
@@ -663,12 +701,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1195,10 +1239,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="1"/>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="41" customWidth="1"/>
+    <col min="1" max="1" width="63.6363636363636" customWidth="1"/>
     <col min="2" max="2" width="37.9090909090909" customWidth="1"/>
     <col min="3" max="3" width="11.9909090909091"/>
     <col min="4" max="4" width="13.6363636363636"/>
@@ -1224,9 +1268,73 @@
         <v>3</v>
       </c>
     </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="2"/>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2"/>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" ht="84" spans="1:2">
+      <c r="A8" s="2"/>
+      <c r="B8" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2"/>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2"/>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2"/>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2"/>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:A3"/>
+    <mergeCell ref="A5:A12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/时间轴照片.xlsx
+++ b/时间轴照片.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Step1：2006-2018——也许我们曾在某处相遇</t>
   </si>
@@ -86,6 +86,48 @@
   </si>
   <si>
     <t>Step4：新生活！关于爱、成长和旅行</t>
+  </si>
+  <si>
+    <t>小薛和小薛的一年四季！</t>
+  </si>
+  <si>
+    <t>混了什么奇怪的东西进来啊喂！！！但是太好笑了谁能拒绝来上这么一张抖音特效！！</t>
+  </si>
+  <si>
+    <t>做完拉直的黑长直学姐/萌萌小蜜蜂/饭撒中......（\学姐/\学姐/\学姐/）/还没长出双眼皮的酷girl（被打）</t>
+  </si>
+  <si>
+    <t>甜酷女孩我亲（又被打）/看起来很暖和的摇粒绒/萌萌发卡（摸头）</t>
+  </si>
+  <si>
+    <t>古早画风QQ头像级别prprpr/齐刘海！拥护齐刘海！/蚊子视角萌之萌之/鱿鱼是一种天赋/滑雪酷girl！/好适合拍耳机广告（喂！）/揉一把帽子上的耳朵</t>
+  </si>
+  <si>
+    <t>总裁提了一辆新车/总裁给老闺比心/总裁の不悦/总裁展示美甲</t>
+  </si>
+  <si>
+    <t>帅气...扑面而来.../&gt;_o/睡前报备中（x）/好困....../姐の冷酷零下八度/小薛得意/好神秘/总裁趁老闺在外与其他女人卿卿我我（不是）（寸不己）（这里有两个人很萌）</t>
+  </si>
+  <si>
+    <t>大连！！！！！！！（想念一些步行三公里边走边聊天......想念在酒店对饮快哉快哉）</t>
+  </si>
+  <si>
+    <t>沈阳！！！！！！！（：魔音贯耳之好绵密呀！好酥脆呀！）</t>
+  </si>
+  <si>
+    <t>北京！！！！！！！很喜欢这个萌萌小财神/很难想象这两个人刚逛完国博/偷拍（被打）/是谁的剪刀手好难猜呀/天坛俺们来了（指）/：就是这个地方把我们累死了！！！</t>
+  </si>
+  <si>
+    <t>好神秘的一组照片......</t>
+  </si>
+  <si>
+    <t>一些你镜头下的我（被人记录着是一件特别幸福的事情......</t>
+  </si>
+  <si>
+    <t>一些很喜欢的神秘视频截屏......鬼迷日眼/傲娇中（左下角有个神秘生物牙飘出来了喂！）/依旧爱饭撒/犹抱琵琶半遮面中.../嘿嘿好萌/嘿嘿好萌/干杯[]~(￣▽￣)~*/这是美神降临......好美丽的打光好飘逸的秀发好美萌的脸好适合拍洗发水广告（喂！！！）</t>
+  </si>
+  <si>
+    <t>这个学姐好美丽可以留个联系方式吗（被打）</t>
   </si>
 </sst>
 </file>
@@ -1239,7 +1281,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="63.6363636363636" customWidth="1"/>
@@ -1327,14 +1369,96 @@
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2"/>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2"/>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="2"/>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2"/>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2"/>
+      <c r="B18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2"/>
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2"/>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2"/>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2"/>
+      <c r="B22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2"/>
+      <c r="B23" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2"/>
+      <c r="B24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2"/>
+      <c r="B25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2"/>
+      <c r="B26" t="s">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="A5:A12"/>
+    <mergeCell ref="A13:A26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
